--- a/report_templates/Installation Pending.xlsx
+++ b/report_templates/Installation Pending.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git hub repositeries\GRP_SYS\report_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/report_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FE735B-6200-4635-A269-EBE8921CFCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{47FE735B-6200-4635-A269-EBE8921CFCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB8B6F73-675E-412B-B700-90BCF7E3DAE4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t xml:space="preserve">           CUSTOMER</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">   LOCATION</t>
   </si>
@@ -39,41 +36,47 @@
     <t xml:space="preserve">  STATUS OF INSTALATION</t>
   </si>
   <si>
-    <t xml:space="preserve">                   REMARKS</t>
-  </si>
-  <si>
     <t>INST.START</t>
   </si>
   <si>
     <t xml:space="preserve">     TANK SIZE</t>
   </si>
   <si>
-    <t xml:space="preserve">                               WORKERS</t>
-  </si>
-  <si>
     <t>W.O.NO.</t>
   </si>
   <si>
     <t xml:space="preserve"> TYPE</t>
   </si>
   <si>
-    <t xml:space="preserve">   CONT.PER.</t>
-  </si>
-  <si>
-    <t>SALES PER.</t>
-  </si>
-  <si>
-    <t>PH. NUMBER</t>
-  </si>
-  <si>
     <t>INS.COMPLET.</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> WORKERS</t>
+  </si>
+  <si>
+    <t>REMARKS</t>
+  </si>
+  <si>
+    <t>PHONE</t>
+  </si>
+  <si>
+    <t>SALES PERSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CONTACT PERSON</t>
+  </si>
+  <si>
+    <t>Qty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,6 +97,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -109,7 +120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -118,17 +129,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
+      <left style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -141,9 +147,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -152,28 +157,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -189,6 +181,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -457,220 +453,205 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.453125" customWidth="1"/>
-    <col min="2" max="2" width="29.81640625" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" style="12" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="48.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.26953125" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" customWidth="1"/>
-    <col min="11" max="11" width="11.81640625" customWidth="1"/>
-    <col min="12" max="12" width="13.26953125" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="43.54296875" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" customWidth="1"/>
+    <col min="6" max="6" width="7.54296875" customWidth="1"/>
+    <col min="7" max="7" width="12.81640625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="38.6328125" customWidth="1"/>
+    <col min="10" max="10" width="40.453125" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" customWidth="1"/>
+    <col min="12" max="12" width="11.81640625" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" customWidth="1"/>
+    <col min="14" max="14" width="19.7265625" customWidth="1"/>
+    <col min="15" max="15" width="45.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="N4" s="4"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="G5" s="3"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="G6" s="3"/>
-      <c r="K6" s="2"/>
-      <c r="N6" s="4"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="G8" s="5"/>
-      <c r="K8" s="2"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="8"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="9"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="9"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="8"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="8"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
-      <c r="F15" s="13"/>
-      <c r="H15"/>
-    </row>
-    <row r="16" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6"/>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="9"/>
-      <c r="H17"/>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6"/>
-      <c r="F18" s="13"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="14"/>
-      <c r="F19" s="15"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="F21" s="15"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="24" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="F24" s="15"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-    </row>
-    <row r="27" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="F27" s="15"/>
-    </row>
-    <row r="28" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="16"/>
-      <c r="F28" s="18"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A29" s="2"/>
-      <c r="G29" s="5"/>
-      <c r="K29" s="2"/>
-      <c r="M29" s="4"/>
-    </row>
-    <row r="30" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="F30" s="15"/>
-      <c r="G30" s="19"/>
-      <c r="P30" s="20"/>
-    </row>
-    <row r="31" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="16"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="21"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A32" s="2"/>
-    </row>
-    <row r="33" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="F33" s="15"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A34" s="2"/>
-      <c r="G34" s="5"/>
-      <c r="M34" s="4"/>
-    </row>
-    <row r="35" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="F35" s="15"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="H5" s="2"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+      <c r="H6" s="2"/>
+      <c r="L6" s="1"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="1"/>
+      <c r="H8" s="4"/>
+      <c r="L8" s="1"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="7"/>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="8"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="8"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5"/>
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="7"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+    </row>
+    <row r="14" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="7"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+    </row>
+    <row r="15" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5"/>
+      <c r="G15" s="10"/>
+      <c r="I15"/>
+    </row>
+    <row r="16" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5"/>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="8"/>
+      <c r="I17"/>
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5"/>
+      <c r="G18" s="10"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A29" s="1"/>
+      <c r="H29" s="4"/>
+      <c r="L29" s="1"/>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="H30" s="4"/>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A31" s="1"/>
+      <c r="H31" s="2"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" s="1"/>
+      <c r="H34" s="4"/>
+      <c r="N34" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/report_templates/Installation Pending.xlsx
+++ b/report_templates/Installation Pending.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/report_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{47FE735B-6200-4635-A269-EBE8921CFCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB8B6F73-675E-412B-B700-90BCF7E3DAE4}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{47FE735B-6200-4635-A269-EBE8921CFCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3591E0B-A078-467C-849D-23EFE5B9FA0A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">   LOCATION</t>
   </si>
@@ -39,18 +39,12 @@
     <t>INST.START</t>
   </si>
   <si>
-    <t xml:space="preserve">     TANK SIZE</t>
-  </si>
-  <si>
     <t>W.O.NO.</t>
   </si>
   <si>
     <t xml:space="preserve"> TYPE</t>
   </si>
   <si>
-    <t>INS.COMPLET.</t>
-  </si>
-  <si>
     <t>CUSTOMER</t>
   </si>
   <si>
@@ -70,6 +64,9 @@
   </si>
   <si>
     <t>Qty</t>
+  </si>
+  <si>
+    <t>TANK SIZE/MATERIAL</t>
   </si>
 </sst>
 </file>
@@ -453,47 +450,46 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.453125" customWidth="1"/>
     <col min="2" max="2" width="28.54296875" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" customWidth="1"/>
-    <col min="5" max="5" width="10.90625" customWidth="1"/>
-    <col min="6" max="6" width="7.54296875" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="30.08984375" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" customWidth="1"/>
+    <col min="7" max="7" width="7.54296875" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="38.6328125" customWidth="1"/>
+    <col min="9" max="9" width="28.26953125" customWidth="1"/>
     <col min="10" max="10" width="40.453125" customWidth="1"/>
     <col min="11" max="11" width="17.453125" customWidth="1"/>
     <col min="12" max="12" width="11.81640625" customWidth="1"/>
-    <col min="13" max="13" width="14.6328125" customWidth="1"/>
-    <col min="14" max="14" width="19.7265625" customWidth="1"/>
-    <col min="15" max="15" width="45.26953125" customWidth="1"/>
+    <col min="13" max="13" width="19.7265625" customWidth="1"/>
+    <col min="14" max="14" width="45.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>5</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>0</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>3</v>
@@ -502,156 +498,148 @@
         <v>2</v>
       </c>
       <c r="J1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>11</v>
-      </c>
       <c r="M1" s="11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="H2" s="1"/>
       <c r="J2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="H5" s="2"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="H6" s="2"/>
       <c r="L6" s="1"/>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="H8" s="4"/>
       <c r="L8" s="1"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
-      <c r="G9" s="10"/>
+      <c r="D9" s="10"/>
       <c r="H9" s="7"/>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="10"/>
       <c r="H10" s="8"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="10"/>
       <c r="H11" s="8"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
-      <c r="G12" s="10"/>
-    </row>
-    <row r="13" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D12" s="10"/>
+    </row>
+    <row r="13" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="10"/>
       <c r="H13" s="7"/>
       <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
-      <c r="G14" s="10"/>
+      <c r="D14" s="10"/>
       <c r="H14" s="7"/>
       <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
-      <c r="G15" s="10"/>
+      <c r="D15" s="10"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D16" s="10"/>
+    </row>
+    <row r="17" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
-      <c r="G17" s="10"/>
+      <c r="D17" s="10"/>
       <c r="H17" s="8"/>
       <c r="I17"/>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
-      <c r="G18" s="10"/>
+      <c r="D18" s="10"/>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="H29" s="4"/>
       <c r="L29" s="1"/>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="H30" s="4"/>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="H31" s="2"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="H34" s="4"/>
-      <c r="N34" s="3"/>
+      <c r="M34" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
